--- a/docs/workbook-split/dateien/Bestände.xlsx
+++ b/docs/workbook-split/dateien/Bestände.xlsx
@@ -712,13 +712,11 @@
       <c r="H7" s="6" t="n">
         <v>760453.65</v>
       </c>
-      <c r="I7" s="6">
-        <f>F7-G7-H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="7">
-        <f>IF(F7=0,"n.a.",(G7+H7)/F7)</f>
-        <v/>
+      <c r="I7" s="6" t="n">
+        <v>-410452.46</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>1.97283035836348</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>51</v>
@@ -773,13 +771,11 @@
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="6">
-        <f>F8-G8-H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="7">
-        <f>IF(F8=0,"n.a.",(G8+H8)/F8)</f>
-        <v/>
+      <c r="I8" s="6" t="n">
+        <v>-10491.03999999999</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>1.086618303382526</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>24</v>
@@ -834,13 +830,11 @@
       <c r="H9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="6">
-        <f>F9-G9-H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="7">
-        <f>IF(F9=0,"n.a.",(G9+H9)/F9)</f>
-        <v/>
+      <c r="I9" s="6" t="n">
+        <v>3310.51</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>0</v>
@@ -891,13 +885,11 @@
       <c r="H10" s="6" t="n">
         <v>-66752</v>
       </c>
-      <c r="I10" s="6">
-        <f>F10-G10-H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="7">
-        <f>IF(F10=0,"n.a.",(G10+H10)/F10)</f>
-        <v/>
+      <c r="I10" s="6" t="n">
+        <v>138.3300000000017</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.2649450023912035</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>12</v>
@@ -952,13 +944,13 @@
       <c r="H11" s="6" t="n">
         <v>-44762.43</v>
       </c>
-      <c r="I11" s="6">
-        <f>F11-G11-H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="7">
-        <f>IF(F11=0,"n.a.",(G11+H11)/F11)</f>
-        <v/>
+      <c r="I11" s="6" t="n">
+        <v>-5236.57</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
@@ -1013,13 +1005,11 @@
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="6">
-        <f>F12-G12-H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="7">
-        <f>IF(F12=0,"n.a.",(G12+H12)/F12)</f>
-        <v/>
+      <c r="I12" s="6" t="n">
+        <v>18183.28</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.5237894701555236</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
@@ -1074,13 +1064,11 @@
       <c r="H13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="6">
-        <f>F13-G13-H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="7">
-        <f>IF(F13=0,"n.a.",(G13+H13)/F13)</f>
-        <v/>
+      <c r="I13" s="6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>0</v>
@@ -1131,13 +1119,11 @@
       <c r="H14" s="6" t="n">
         <v>2029184.6</v>
       </c>
-      <c r="I14" s="6">
-        <f>F14-G14-H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="7">
-        <f>IF(F14=0,"n.a.",(G14+H14)/F14)</f>
-        <v/>
+      <c r="I14" s="6" t="n">
+        <v>-267232.4299999999</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>1.148289204124157</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>140</v>
@@ -1192,13 +1178,11 @@
       <c r="H15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="6">
-        <f>F15-G15-H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="7">
-        <f>IF(F15=0,"n.a.",(G15+H15)/F15)</f>
-        <v/>
+      <c r="I15" s="6" t="n">
+        <v>-73956.17999999999</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>4.073692636471771</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>61</v>
@@ -1253,13 +1237,11 @@
       <c r="H16" s="6" t="n">
         <v>1969.8</v>
       </c>
-      <c r="I16" s="6">
-        <f>F16-G16-H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="7">
-        <f>IF(F16=0,"n.a.",(G16+H16)/F16)</f>
-        <v/>
+      <c r="I16" s="6" t="n">
+        <v>-211.05</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>1.12</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>0</v>
@@ -1310,13 +1292,11 @@
       <c r="H17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="6">
-        <f>F17-G17-H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="7">
-        <f>IF(F17=0,"n.a.",(G17+H17)/F17)</f>
-        <v/>
+      <c r="I17" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>0</v>
@@ -1367,13 +1347,11 @@
       <c r="H18" s="6" t="n">
         <v>-870769.6</v>
       </c>
-      <c r="I18" s="6">
-        <f>F18-G18-H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="7">
-        <f>IF(F18=0,"n.a.",(G18+H18)/F18)</f>
-        <v/>
+      <c r="I18" s="6" t="n">
+        <v>-798050.6599999998</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>1.363898545470377</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>35</v>
@@ -1428,13 +1406,13 @@
       <c r="H19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="6">
-        <f>F19-G19-H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="7">
-        <f>IF(F19=0,"n.a.",(G19+H19)/F19)</f>
-        <v/>
+      <c r="I19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K19" s="1" t="n">
         <v>0</v>
@@ -1483,13 +1461,11 @@
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="6">
-        <f>F20-G20-H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="7">
-        <f>IF(F20=0,"n.a.",(G20+H20)/F20)</f>
-        <v/>
+      <c r="I20" s="6" t="n">
+        <v>166.84</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>0</v>
@@ -1540,13 +1516,11 @@
       <c r="H21" s="6" t="n">
         <v>-71121.52</v>
       </c>
-      <c r="I21" s="6">
-        <f>F21-G21-H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="7">
-        <f>IF(F21=0,"n.a.",(G21+H21)/F21)</f>
-        <v/>
+      <c r="I21" s="6" t="n">
+        <v>-1339.62999999999</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.9718600596563459</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>10</v>
@@ -1601,13 +1575,11 @@
       <c r="H22" s="6" t="n">
         <v>211492.24</v>
       </c>
-      <c r="I22" s="6">
-        <f>F22-G22-H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="7">
-        <f>IF(F22=0,"n.a.",(G22+H22)/F22)</f>
-        <v/>
+      <c r="I22" s="6" t="n">
+        <v>103167.02</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.880268460326417</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>8</v>
@@ -1662,13 +1634,11 @@
       <c r="H23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="6">
-        <f>F23-G23-H23</f>
-        <v/>
-      </c>
-      <c r="J23" s="7">
-        <f>IF(F23=0,"n.a.",(G23+H23)/F23)</f>
-        <v/>
+      <c r="I23" s="6" t="n">
+        <v>-8788.820000000003</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>1.279476485208335</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>3</v>
@@ -1723,13 +1693,11 @@
       <c r="H24" s="6" t="n">
         <v>-279004.22</v>
       </c>
-      <c r="I24" s="6">
-        <f>F24-G24-H24</f>
-        <v/>
-      </c>
-      <c r="J24" s="7">
-        <f>IF(F24=0,"n.a.",(G24+H24)/F24)</f>
-        <v/>
+      <c r="I24" s="6" t="n">
+        <v>-35088.55000000005</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>1.347813403333715</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
@@ -1784,13 +1752,11 @@
       <c r="H25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="6">
-        <f>F25-G25-H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="7">
-        <f>IF(F25=0,"n.a.",(G25+H25)/F25)</f>
-        <v/>
+      <c r="I25" s="6" t="n">
+        <v>-4201.349999999977</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>1.004994438636973</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>42</v>
@@ -1845,13 +1811,11 @@
       <c r="H26" s="6" t="n">
         <v>2639009.53</v>
       </c>
-      <c r="I26" s="6">
-        <f>F26-G26-H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="7">
-        <f>IF(F26=0,"n.a.",(G26+H26)/F26)</f>
-        <v/>
+      <c r="I26" s="6" t="n">
+        <v>157046.5300000003</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.9438328393172488</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>54</v>
@@ -1906,13 +1870,13 @@
       <c r="H27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="6">
-        <f>F27-G27-H27</f>
-        <v/>
-      </c>
-      <c r="J27" s="7">
-        <f>IF(F27=0,"n.a.",(G27+H27)/F27)</f>
-        <v/>
+      <c r="I27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K27" s="1" t="n">
         <v>0</v>
@@ -1963,13 +1927,11 @@
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="6">
-        <f>F28-G28-H28</f>
-        <v/>
-      </c>
-      <c r="J28" s="7">
-        <f>IF(F28=0,"n.a.",(G28+H28)/F28)</f>
-        <v/>
+      <c r="I28" s="6" t="n">
+        <v>-26604.17</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>1.279545186124796</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>4</v>
@@ -2024,13 +1986,13 @@
       <c r="H29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="6">
-        <f>F29-G29-H29</f>
-        <v/>
-      </c>
-      <c r="J29" s="7">
-        <f>IF(F29=0,"n.a.",(G29+H29)/F29)</f>
-        <v/>
+      <c r="I29" s="6" t="n">
+        <v>-6059.53</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K29" s="1" t="n">
         <v>1</v>
@@ -2085,13 +2047,11 @@
       <c r="H30" s="6" t="n">
         <v>-168400.34</v>
       </c>
-      <c r="I30" s="6">
-        <f>F30-G30-H30</f>
-        <v/>
-      </c>
-      <c r="J30" s="7">
-        <f>IF(F30=0,"n.a.",(G30+H30)/F30)</f>
-        <v/>
+      <c r="I30" s="6" t="n">
+        <v>70340.19</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.5071116850792725</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>21</v>
@@ -2146,13 +2106,11 @@
       <c r="H31" s="6" t="n">
         <v>475.29</v>
       </c>
-      <c r="I31" s="6">
-        <f>F31-G31-H31</f>
-        <v/>
-      </c>
-      <c r="J31" s="7">
-        <f>IF(F31=0,"n.a.",(G31+H31)/F31)</f>
-        <v/>
+      <c r="I31" s="6" t="n">
+        <v>-50.92000000000002</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>1.119989631689328</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>0</v>
@@ -2203,13 +2161,11 @@
       <c r="H32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="6">
-        <f>F32-G32-H32</f>
-        <v/>
-      </c>
-      <c r="J32" s="7">
-        <f>IF(F32=0,"n.a.",(G32+H32)/F32)</f>
-        <v/>
+      <c r="I32" s="6" t="n">
+        <v>-22533.26</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>2.161397495599647</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>4</v>
@@ -2264,13 +2220,11 @@
       <c r="H33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="6">
-        <f>F33-G33-H33</f>
-        <v/>
-      </c>
-      <c r="J33" s="7">
-        <f>IF(F33=0,"n.a.",(G33+H33)/F33)</f>
-        <v/>
+      <c r="I33" s="6" t="n">
+        <v>-8155.800000000003</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>1.406399301589959</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>2</v>
@@ -2325,13 +2279,11 @@
       <c r="H34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="6">
-        <f>F34-G34-H34</f>
-        <v/>
-      </c>
-      <c r="J34" s="7">
-        <f>IF(F34=0,"n.a.",(G34+H34)/F34)</f>
-        <v/>
+      <c r="I34" s="6" t="n">
+        <v>22810.75999999999</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.6401021122982841</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>2</v>
@@ -2386,13 +2338,13 @@
       <c r="H35" s="6" t="n">
         <v>-25780.46</v>
       </c>
-      <c r="I35" s="6">
-        <f>F35-G35-H35</f>
-        <v/>
-      </c>
-      <c r="J35" s="7">
-        <f>IF(F35=0,"n.a.",(G35+H35)/F35)</f>
-        <v/>
+      <c r="I35" s="6" t="n">
+        <v>25780.46</v>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K35" s="1" t="n">
         <v>0</v>
@@ -2441,13 +2393,13 @@
       <c r="H36" s="6" t="n">
         <v>-2847.73</v>
       </c>
-      <c r="I36" s="6">
-        <f>F36-G36-H36</f>
-        <v/>
-      </c>
-      <c r="J36" s="7">
-        <f>IF(F36=0,"n.a.",(G36+H36)/F36)</f>
-        <v/>
+      <c r="I36" s="6" t="n">
+        <v>2847.73</v>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K36" s="1" t="n">
         <v>0</v>
@@ -2496,13 +2448,11 @@
       <c r="H37" s="6" t="n">
         <v>-46621</v>
       </c>
-      <c r="I37" s="6">
-        <f>F37-G37-H37</f>
-        <v/>
-      </c>
-      <c r="J37" s="7">
-        <f>IF(F37=0,"n.a.",(G37+H37)/F37)</f>
-        <v/>
+      <c r="I37" s="6" t="n">
+        <v>8125.379999999997</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>0.6316427015171532</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>3</v>
@@ -2557,13 +2507,11 @@
       <c r="H38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="6">
-        <f>F38-G38-H38</f>
-        <v/>
-      </c>
-      <c r="J38" s="7">
-        <f>IF(F38=0,"n.a.",(G38+H38)/F38)</f>
-        <v/>
+      <c r="I38" s="6" t="n">
+        <v>-10121.36</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>1.082705282555845</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>1</v>
@@ -2618,13 +2566,11 @@
       <c r="H39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="6">
-        <f>F39-G39-H39</f>
-        <v/>
-      </c>
-      <c r="J39" s="7">
-        <f>IF(F39=0,"n.a.",(G39+H39)/F39)</f>
-        <v/>
+      <c r="I39" s="6" t="n">
+        <v>400.43</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K39" s="1" t="n">
         <v>0</v>
@@ -2675,13 +2621,11 @@
       <c r="H40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="6">
-        <f>F40-G40-H40</f>
-        <v/>
-      </c>
-      <c r="J40" s="7">
-        <f>IF(F40=0,"n.a.",(G40+H40)/F40)</f>
-        <v/>
+      <c r="I40" s="6" t="n">
+        <v>35296.25999999999</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>-0.4292147879881407</v>
       </c>
       <c r="K40" s="1" t="n">
         <v>1</v>
@@ -2736,13 +2680,11 @@
       <c r="H41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="6">
-        <f>F41-G41-H41</f>
-        <v/>
-      </c>
-      <c r="J41" s="7">
-        <f>IF(F41=0,"n.a.",(G41+H41)/F41)</f>
-        <v/>
+      <c r="I41" s="6" t="n">
+        <v>-2000.009999999999</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>1.271480074819535</v>
       </c>
       <c r="K41" s="1" t="n">
         <v>1</v>
@@ -2797,13 +2739,11 @@
       <c r="H42" s="6" t="n">
         <v>124.87</v>
       </c>
-      <c r="I42" s="6">
-        <f>F42-G42-H42</f>
-        <v/>
-      </c>
-      <c r="J42" s="7">
-        <f>IF(F42=0,"n.a.",(G42+H42)/F42)</f>
-        <v/>
+      <c r="I42" s="6" t="n">
+        <v>1212.92</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0.09339472445005868</v>
       </c>
       <c r="K42" s="1" t="n">
         <v>13</v>
@@ -2858,13 +2798,11 @@
       <c r="H43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="6">
-        <f>F43-G43-H43</f>
-        <v/>
-      </c>
-      <c r="J43" s="7">
-        <f>IF(F43=0,"n.a.",(G43+H43)/F43)</f>
-        <v/>
+      <c r="I43" s="6" t="n">
+        <v>8020.540000000001</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>0.6930281120624557</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>9</v>
@@ -2919,13 +2857,11 @@
       <c r="H44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="6">
-        <f>F44-G44-H44</f>
-        <v/>
-      </c>
-      <c r="J44" s="7">
-        <f>IF(F44=0,"n.a.",(G44+H44)/F44)</f>
-        <v/>
+      <c r="I44" s="6" t="n">
+        <v>-7057.91</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>1.86155181400595</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>1</v>
@@ -2980,13 +2916,13 @@
       <c r="H45" s="6" t="n">
         <v>-13730.16</v>
       </c>
-      <c r="I45" s="6">
-        <f>F45-G45-H45</f>
-        <v/>
-      </c>
-      <c r="J45" s="7">
-        <f>IF(F45=0,"n.a.",(G45+H45)/F45)</f>
-        <v/>
+      <c r="I45" s="6" t="n">
+        <v>-7269.84</v>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K45" s="1" t="n">
         <v>1</v>
@@ -3041,13 +2977,11 @@
       <c r="H46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="6">
-        <f>F46-G46-H46</f>
-        <v/>
-      </c>
-      <c r="J46" s="7">
-        <f>IF(F46=0,"n.a.",(G46+H46)/F46)</f>
-        <v/>
+      <c r="I46" s="6" t="n">
+        <v>-33286.16</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>1.475558420569582</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>9</v>
@@ -3102,13 +3036,13 @@
       <c r="H47" s="6" t="n">
         <v>-24683.12</v>
       </c>
-      <c r="I47" s="6">
-        <f>F47-G47-H47</f>
-        <v/>
-      </c>
-      <c r="J47" s="7">
-        <f>IF(F47=0,"n.a.",(G47+H47)/F47)</f>
-        <v/>
+      <c r="I47" s="6" t="n">
+        <v>5683.119999999999</v>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K47" s="1" t="n">
         <v>1</v>
@@ -3163,13 +3097,11 @@
       <c r="H48" s="6" t="n">
         <v>5723.3</v>
       </c>
-      <c r="I48" s="6">
-        <f>F48-G48-H48</f>
-        <v/>
-      </c>
-      <c r="J48" s="7">
-        <f>IF(F48=0,"n.a.",(G48+H48)/F48)</f>
-        <v/>
+      <c r="I48" s="6" t="n">
+        <v>-1289.009999999999</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>1.022913138547688</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>15</v>
@@ -3224,13 +3156,11 @@
       <c r="H49" s="6" t="n">
         <v>-39732.85</v>
       </c>
-      <c r="I49" s="6">
-        <f>F49-G49-H49</f>
-        <v/>
-      </c>
-      <c r="J49" s="7">
-        <f>IF(F49=0,"n.a.",(G49+H49)/F49)</f>
-        <v/>
+      <c r="I49" s="6" t="n">
+        <v>-14925.16</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>1.487750326797386</v>
       </c>
       <c r="K49" s="1" t="n">
         <v>13</v>
@@ -3285,13 +3215,13 @@
       <c r="H50" s="6" t="n">
         <v>-44321.39</v>
       </c>
-      <c r="I50" s="6">
-        <f>F50-G50-H50</f>
-        <v/>
-      </c>
-      <c r="J50" s="7">
-        <f>IF(F50=0,"n.a.",(G50+H50)/F50)</f>
-        <v/>
+      <c r="I50" s="6" t="n">
+        <v>-81006.27</v>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K50" s="1" t="n">
         <v>1</v>
@@ -3346,13 +3276,11 @@
       <c r="H51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="6">
-        <f>F51-G51-H51</f>
-        <v/>
-      </c>
-      <c r="J51" s="7">
-        <f>IF(F51=0,"n.a.",(G51+H51)/F51)</f>
-        <v/>
+      <c r="I51" s="6" t="n">
+        <v>-139734.82</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>2.045896060544163</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>44</v>
@@ -3407,13 +3335,11 @@
       <c r="H52" s="6" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I52" s="6">
-        <f>F52-G52-H52</f>
-        <v/>
-      </c>
-      <c r="J52" s="7">
-        <f>IF(F52=0,"n.a.",(G52+H52)/F52)</f>
-        <v/>
+      <c r="I52" s="6" t="n">
+        <v>-474040.0399999999</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>1.806459514924272</v>
       </c>
       <c r="K52" s="1" t="n">
         <v>18</v>
@@ -3468,13 +3394,11 @@
       <c r="H53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="6">
-        <f>F53-G53-H53</f>
-        <v/>
-      </c>
-      <c r="J53" s="7">
-        <f>IF(F53=0,"n.a.",(G53+H53)/F53)</f>
-        <v/>
+      <c r="I53" s="6" t="n">
+        <v>-13322.18</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>5.919473421834899</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>12</v>
@@ -3529,13 +3453,11 @@
       <c r="H54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I54" s="6">
-        <f>F54-G54-H54</f>
-        <v/>
-      </c>
-      <c r="J54" s="7">
-        <f>IF(F54=0,"n.a.",(G54+H54)/F54)</f>
-        <v/>
+      <c r="I54" s="6" t="n">
+        <v>-4915.35</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>0</v>
@@ -3586,13 +3508,11 @@
       <c r="H55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="6">
-        <f>F55-G55-H55</f>
-        <v/>
-      </c>
-      <c r="J55" s="7">
-        <f>IF(F55=0,"n.a.",(G55+H55)/F55)</f>
-        <v/>
+      <c r="I55" s="6" t="n">
+        <v>161181.74</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>0.2480315392266192</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>4</v>
@@ -3647,13 +3567,11 @@
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="6">
-        <f>F56-G56-H56</f>
-        <v/>
-      </c>
-      <c r="J56" s="7">
-        <f>IF(F56=0,"n.a.",(G56+H56)/F56)</f>
-        <v/>
+      <c r="I56" s="6" t="n">
+        <v>1091.42</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>4</v>
@@ -3708,13 +3626,11 @@
       <c r="H57" s="6" t="n">
         <v>-70767.05</v>
       </c>
-      <c r="I57" s="6">
-        <f>F57-G57-H57</f>
-        <v/>
-      </c>
-      <c r="J57" s="7">
-        <f>IF(F57=0,"n.a.",(G57+H57)/F57)</f>
-        <v/>
+      <c r="I57" s="6" t="n">
+        <v>-171705.63</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>3.852284260923792</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>21</v>
@@ -3769,13 +3685,13 @@
       <c r="H58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="6">
-        <f>F58-G58-H58</f>
-        <v/>
-      </c>
-      <c r="J58" s="7">
-        <f>IF(F58=0,"n.a.",(G58+H58)/F58)</f>
-        <v/>
+      <c r="I58" s="6" t="n">
+        <v>-37284</v>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K58" s="1" t="n">
         <v>1</v>
@@ -3830,13 +3746,11 @@
       <c r="H59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="6">
-        <f>F59-G59-H59</f>
-        <v/>
-      </c>
-      <c r="J59" s="7">
-        <f>IF(F59=0,"n.a.",(G59+H59)/F59)</f>
-        <v/>
+      <c r="I59" s="6" t="n">
+        <v>583.34</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>0</v>
@@ -3887,13 +3801,13 @@
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I60" s="6">
-        <f>F60-G60-H60</f>
-        <v/>
-      </c>
-      <c r="J60" s="7">
-        <f>IF(F60=0,"n.a.",(G60+H60)/F60)</f>
-        <v/>
+      <c r="I60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K60" s="1" t="n">
         <v>0</v>
@@ -3940,13 +3854,13 @@
       <c r="H61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="9">
-        <f>F61-G61-H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="10">
-        <f>IF(F61=0,"n.a.",(G61+H61)/F61)</f>
-        <v/>
+      <c r="I61" s="9" t="n">
+        <v>-8250</v>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K61" s="8" t="n">
         <v>1</v>
@@ -3998,13 +3912,11 @@
       <c r="H62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="9">
-        <f>F62-G62-H62</f>
-        <v/>
-      </c>
-      <c r="J62" s="10">
-        <f>IF(F62=0,"n.a.",(G62+H62)/F62)</f>
-        <v/>
+      <c r="I62" s="9" t="n">
+        <v>3096.72</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K62" s="8" t="n">
         <v>0</v>
@@ -4052,13 +3964,11 @@
       <c r="H63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="9">
-        <f>F63-G63-H63</f>
-        <v/>
-      </c>
-      <c r="J63" s="10">
-        <f>IF(F63=0,"n.a.",(G63+H63)/F63)</f>
-        <v/>
+      <c r="I63" s="9" t="n">
+        <v>-81274.25999999999</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>5.483013759985173</v>
       </c>
       <c r="K63" s="8" t="n">
         <v>6</v>
@@ -4110,13 +4020,11 @@
       <c r="H64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I64" s="9">
-        <f>F64-G64-H64</f>
-        <v/>
-      </c>
-      <c r="J64" s="10">
-        <f>IF(F64=0,"n.a.",(G64+H64)/F64)</f>
-        <v/>
+      <c r="I64" s="9" t="n">
+        <v>-8632.59</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>1.547128279883382</v>
       </c>
       <c r="K64" s="8" t="n">
         <v>3</v>
@@ -4168,13 +4076,11 @@
       <c r="H65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I65" s="9">
-        <f>F65-G65-H65</f>
-        <v/>
-      </c>
-      <c r="J65" s="10">
-        <f>IF(F65=0,"n.a.",(G65+H65)/F65)</f>
-        <v/>
+      <c r="I65" s="9" t="n">
+        <v>-142168.39</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>20.29575073359157</v>
       </c>
       <c r="K65" s="8" t="n">
         <v>4</v>
@@ -4226,13 +4132,11 @@
       <c r="H66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I66" s="9">
-        <f>F66-G66-H66</f>
-        <v/>
-      </c>
-      <c r="J66" s="10">
-        <f>IF(F66=0,"n.a.",(G66+H66)/F66)</f>
-        <v/>
+      <c r="I66" s="9" t="n">
+        <v>5293.57</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K66" s="8" t="n">
         <v>0</v>
@@ -4280,13 +4184,11 @@
       <c r="H67" s="9" t="n">
         <v>78085.17999999999</v>
       </c>
-      <c r="I67" s="9">
-        <f>F67-G67-H67</f>
-        <v/>
-      </c>
-      <c r="J67" s="10">
-        <f>IF(F67=0,"n.a.",(G67+H67)/F67)</f>
-        <v/>
+      <c r="I67" s="9" t="n">
+        <v>-18318.66999999998</v>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>1.275799639898759</v>
       </c>
       <c r="K67" s="8" t="n">
         <v>7</v>
@@ -4338,13 +4240,11 @@
       <c r="H68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I68" s="9">
-        <f>F68-G68-H68</f>
-        <v/>
-      </c>
-      <c r="J68" s="10">
-        <f>IF(F68=0,"n.a.",(G68+H68)/F68)</f>
-        <v/>
+      <c r="I68" s="9" t="n">
+        <v>-7882.97</v>
+      </c>
+      <c r="J68" s="10" t="n">
+        <v>1.971164329810288</v>
       </c>
       <c r="K68" s="8" t="n">
         <v>1</v>
@@ -4396,13 +4296,11 @@
       <c r="H69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="9">
-        <f>F69-G69-H69</f>
-        <v/>
-      </c>
-      <c r="J69" s="10">
-        <f>IF(F69=0,"n.a.",(G69+H69)/F69)</f>
-        <v/>
+      <c r="I69" s="9" t="n">
+        <v>39800.73</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>4438.093645484949</v>
       </c>
       <c r="K69" s="8" t="n">
         <v>1</v>
@@ -4454,13 +4352,13 @@
       <c r="H70" s="9" t="n">
         <v>-6447.83</v>
       </c>
-      <c r="I70" s="9">
-        <f>F70-G70-H70</f>
-        <v/>
-      </c>
-      <c r="J70" s="10">
-        <f>IF(F70=0,"n.a.",(G70+H70)/F70)</f>
-        <v/>
+      <c r="I70" s="9" t="n">
+        <v>6447.83</v>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K70" s="8" t="n">
         <v>0</v>
@@ -4506,13 +4404,11 @@
       <c r="H71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="9">
-        <f>F71-G71-H71</f>
-        <v/>
-      </c>
-      <c r="J71" s="10">
-        <f>IF(F71=0,"n.a.",(G71+H71)/F71)</f>
-        <v/>
+      <c r="I71" s="9" t="n">
+        <v>59788.76000000001</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>1.949077650099132</v>
       </c>
       <c r="K71" s="8" t="n">
         <v>2</v>
@@ -4564,13 +4460,11 @@
       <c r="H72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I72" s="9">
-        <f>F72-G72-H72</f>
-        <v/>
-      </c>
-      <c r="J72" s="10">
-        <f>IF(F72=0,"n.a.",(G72+H72)/F72)</f>
-        <v/>
+      <c r="I72" s="9" t="n">
+        <v>870.8399999999999</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>-2.120954736049887</v>
       </c>
       <c r="K72" s="8" t="n">
         <v>1</v>
@@ -4622,13 +4516,13 @@
       <c r="H73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="9">
-        <f>F73-G73-H73</f>
-        <v/>
-      </c>
-      <c r="J73" s="10">
-        <f>IF(F73=0,"n.a.",(G73+H73)/F73)</f>
-        <v/>
+      <c r="I73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K73" s="8" t="n">
         <v>0</v>
@@ -4674,13 +4568,11 @@
       <c r="H74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="9">
-        <f>F74-G74-H74</f>
-        <v/>
-      </c>
-      <c r="J74" s="10">
-        <f>IF(F74=0,"n.a.",(G74+H74)/F74)</f>
-        <v/>
+      <c r="I74" s="9" t="n">
+        <v>-8014.889999999999</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>1.324015518999941</v>
       </c>
       <c r="K74" s="8" t="n">
         <v>1</v>
@@ -4732,13 +4624,11 @@
       <c r="H75" s="9" t="n">
         <v>59.31</v>
       </c>
-      <c r="I75" s="9">
-        <f>F75-G75-H75</f>
-        <v/>
-      </c>
-      <c r="J75" s="10">
-        <f>IF(F75=0,"n.a.",(G75+H75)/F75)</f>
-        <v/>
+      <c r="I75" s="9" t="n">
+        <v>-83.51000000000001</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>-2.450826446280992</v>
       </c>
       <c r="K75" s="8" t="n">
         <v>16</v>
@@ -4790,13 +4680,11 @@
       <c r="H76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I76" s="9">
-        <f>F76-G76-H76</f>
-        <v/>
-      </c>
-      <c r="J76" s="10">
-        <f>IF(F76=0,"n.a.",(G76+H76)/F76)</f>
-        <v/>
+      <c r="I76" s="9" t="n">
+        <v>-36018.06</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>-11.43077974384726</v>
       </c>
       <c r="K76" s="8" t="n">
         <v>4</v>
@@ -4848,13 +4736,11 @@
       <c r="H77" s="9" t="n">
         <v>48667.01</v>
       </c>
-      <c r="I77" s="9">
-        <f>F77-G77-H77</f>
-        <v/>
-      </c>
-      <c r="J77" s="10">
-        <f>IF(F77=0,"n.a.",(G77+H77)/F77)</f>
-        <v/>
+      <c r="I77" s="9" t="n">
+        <v>-16235.65</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>1.354566352246858</v>
       </c>
       <c r="K77" s="8" t="n">
         <v>11</v>
@@ -4906,13 +4792,11 @@
       <c r="H78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="9">
-        <f>F78-G78-H78</f>
-        <v/>
-      </c>
-      <c r="J78" s="10">
-        <f>IF(F78=0,"n.a.",(G78+H78)/F78)</f>
-        <v/>
+      <c r="I78" s="9" t="n">
+        <v>-162063.93</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>-29.53851516995894</v>
       </c>
       <c r="K78" s="8" t="n">
         <v>4</v>
@@ -4964,13 +4848,11 @@
       <c r="H79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="9">
-        <f>F79-G79-H79</f>
-        <v/>
-      </c>
-      <c r="J79" s="10">
-        <f>IF(F79=0,"n.a.",(G79+H79)/F79)</f>
-        <v/>
+      <c r="I79" s="9" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K79" s="8" t="n">
         <v>0</v>
@@ -5018,13 +4900,11 @@
       <c r="H80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I80" s="9">
-        <f>F80-G80-H80</f>
-        <v/>
-      </c>
-      <c r="J80" s="10">
-        <f>IF(F80=0,"n.a.",(G80+H80)/F80)</f>
-        <v/>
+      <c r="I80" s="9" t="n">
+        <v>34350.28999999999</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>0.680820315527129</v>
       </c>
       <c r="K80" s="8" t="n">
         <v>4</v>
@@ -5076,13 +4956,11 @@
       <c r="H81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="9">
-        <f>F81-G81-H81</f>
-        <v/>
-      </c>
-      <c r="J81" s="10">
-        <f>IF(F81=0,"n.a.",(G81+H81)/F81)</f>
-        <v/>
+      <c r="I81" s="9" t="n">
+        <v>-16150.88</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K81" s="8" t="n">
         <v>0</v>
@@ -5130,13 +5008,11 @@
       <c r="H82" s="9" t="n">
         <v>514521.48</v>
       </c>
-      <c r="I82" s="9">
-        <f>F82-G82-H82</f>
-        <v/>
-      </c>
-      <c r="J82" s="10">
-        <f>IF(F82=0,"n.a.",(G82+H82)/F82)</f>
-        <v/>
+      <c r="I82" s="9" t="n">
+        <v>-27803.63999999996</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>1.055650170699562</v>
       </c>
       <c r="K82" s="8" t="n">
         <v>36</v>
@@ -5188,13 +5064,13 @@
       <c r="H83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="9">
-        <f>F83-G83-H83</f>
-        <v/>
-      </c>
-      <c r="J83" s="10">
-        <f>IF(F83=0,"n.a.",(G83+H83)/F83)</f>
-        <v/>
+      <c r="I83" s="9" t="n">
+        <v>-45582.42</v>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K83" s="8" t="n">
         <v>1</v>
@@ -5246,13 +5122,11 @@
       <c r="H84" s="9" t="n">
         <v>-10353.48</v>
       </c>
-      <c r="I84" s="9">
-        <f>F84-G84-H84</f>
-        <v/>
-      </c>
-      <c r="J84" s="10">
-        <f>IF(F84=0,"n.a.",(G84+H84)/F84)</f>
-        <v/>
+      <c r="I84" s="9" t="n">
+        <v>26735.61</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>-0.4856863897894247</v>
       </c>
       <c r="K84" s="8" t="n">
         <v>2</v>
@@ -5304,13 +5178,13 @@
       <c r="H85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I85" s="9">
-        <f>F85-G85-H85</f>
-        <v/>
-      </c>
-      <c r="J85" s="10">
-        <f>IF(F85=0,"n.a.",(G85+H85)/F85)</f>
-        <v/>
+      <c r="I85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K85" s="8" t="n">
         <v>2</v>
@@ -5362,13 +5236,11 @@
       <c r="H86" s="9" t="n">
         <v>9610.309999999999</v>
       </c>
-      <c r="I86" s="9">
-        <f>F86-G86-H86</f>
-        <v/>
-      </c>
-      <c r="J86" s="10">
-        <f>IF(F86=0,"n.a.",(G86+H86)/F86)</f>
-        <v/>
+      <c r="I86" s="9" t="n">
+        <v>-49841.05</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>23.04439304006298</v>
       </c>
       <c r="K86" s="8" t="n">
         <v>7</v>
@@ -5420,13 +5292,11 @@
       <c r="H87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="9">
-        <f>F87-G87-H87</f>
-        <v/>
-      </c>
-      <c r="J87" s="10">
-        <f>IF(F87=0,"n.a.",(G87+H87)/F87)</f>
-        <v/>
+      <c r="I87" s="9" t="n">
+        <v>-7779.879999999999</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>1.487304824517448</v>
       </c>
       <c r="K87" s="8" t="n">
         <v>2</v>
@@ -5478,13 +5348,11 @@
       <c r="H88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="9">
-        <f>F88-G88-H88</f>
-        <v/>
-      </c>
-      <c r="J88" s="10">
-        <f>IF(F88=0,"n.a.",(G88+H88)/F88)</f>
-        <v/>
+      <c r="I88" s="9" t="n">
+        <v>-122000</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>2.244897959183673</v>
       </c>
       <c r="K88" s="8" t="n">
         <v>2</v>
@@ -5536,13 +5404,11 @@
       <c r="H89" s="9" t="n">
         <v>-578657.23</v>
       </c>
-      <c r="I89" s="9">
-        <f>F89-G89-H89</f>
-        <v/>
-      </c>
-      <c r="J89" s="10">
-        <f>IF(F89=0,"n.a.",(G89+H89)/F89)</f>
-        <v/>
+      <c r="I89" s="9" t="n">
+        <v>-110634.3500000001</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>1.802367234765975</v>
       </c>
       <c r="K89" s="8" t="n">
         <v>14</v>
@@ -5594,13 +5460,11 @@
       <c r="H90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="9">
-        <f>F90-G90-H90</f>
-        <v/>
-      </c>
-      <c r="J90" s="10">
-        <f>IF(F90=0,"n.a.",(G90+H90)/F90)</f>
-        <v/>
+      <c r="I90" s="9" t="n">
+        <v>-34662.12</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>-0.5729305497886474</v>
       </c>
       <c r="K90" s="8" t="n">
         <v>2</v>
@@ -5652,13 +5516,13 @@
       <c r="H91" s="9" t="n">
         <v>-83199.77</v>
       </c>
-      <c r="I91" s="9">
-        <f>F91-G91-H91</f>
-        <v/>
-      </c>
-      <c r="J91" s="10">
-        <f>IF(F91=0,"n.a.",(G91+H91)/F91)</f>
-        <v/>
+      <c r="I91" s="9" t="n">
+        <v>-14290.34</v>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="K91" s="8" t="n">
         <v>1</v>
@@ -5710,13 +5574,11 @@
       <c r="H92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I92" s="9">
-        <f>F92-G92-H92</f>
-        <v/>
-      </c>
-      <c r="J92" s="10">
-        <f>IF(F92=0,"n.a.",(G92+H92)/F92)</f>
-        <v/>
+      <c r="I92" s="9" t="n">
+        <v>-16619.55</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>2.044043232852445</v>
       </c>
       <c r="K92" s="8" t="n">
         <v>1</v>
@@ -5768,13 +5630,11 @@
       <c r="H93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I93" s="9">
-        <f>F93-G93-H93</f>
-        <v/>
-      </c>
-      <c r="J93" s="10">
-        <f>IF(F93=0,"n.a.",(G93+H93)/F93)</f>
-        <v/>
+      <c r="I93" s="9" t="n">
+        <v>-19525.49000000001</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>2.122337138741532</v>
       </c>
       <c r="K93" s="8" t="n">
         <v>6</v>
@@ -5826,13 +5686,11 @@
       <c r="H94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I94" s="9">
-        <f>F94-G94-H94</f>
-        <v/>
-      </c>
-      <c r="J94" s="10">
-        <f>IF(F94=0,"n.a.",(G94+H94)/F94)</f>
-        <v/>
+      <c r="I94" s="9" t="n">
+        <v>8715.890000000001</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>0.108040427278179</v>
       </c>
       <c r="K94" s="8" t="n">
         <v>1</v>
@@ -5884,13 +5742,11 @@
       <c r="H95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I95" s="9">
-        <f>F95-G95-H95</f>
-        <v/>
-      </c>
-      <c r="J95" s="10">
-        <f>IF(F95=0,"n.a.",(G95+H95)/F95)</f>
-        <v/>
+      <c r="I95" s="9" t="n">
+        <v>-14874.74</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K95" s="8" t="n">
         <v>0</v>
@@ -5938,13 +5794,11 @@
       <c r="H96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I96" s="9">
-        <f>F96-G96-H96</f>
-        <v/>
-      </c>
-      <c r="J96" s="10">
-        <f>IF(F96=0,"n.a.",(G96+H96)/F96)</f>
-        <v/>
+      <c r="I96" s="9" t="n">
+        <v>-4986.26</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>9.960841045916075</v>
       </c>
       <c r="K96" s="8" t="n">
         <v>3</v>
@@ -5996,13 +5850,11 @@
       <c r="H97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I97" s="9">
-        <f>F97-G97-H97</f>
-        <v/>
-      </c>
-      <c r="J97" s="10">
-        <f>IF(F97=0,"n.a.",(G97+H97)/F97)</f>
-        <v/>
+      <c r="I97" s="9" t="n">
+        <v>1244.98</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>0.9598393548387097</v>
       </c>
       <c r="K97" s="8" t="n">
         <v>3</v>
@@ -6054,13 +5906,11 @@
       <c r="H98" s="9" t="n">
         <v>70709.82000000001</v>
       </c>
-      <c r="I98" s="9">
-        <f>F98-G98-H98</f>
-        <v/>
-      </c>
-      <c r="J98" s="10">
-        <f>IF(F98=0,"n.a.",(G98+H98)/F98)</f>
-        <v/>
+      <c r="I98" s="9" t="n">
+        <v>-67840</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>3.247632514734351</v>
       </c>
       <c r="K98" s="8" t="n">
         <v>6</v>
@@ -6112,13 +5962,11 @@
       <c r="H99" s="9" t="n">
         <v>-35814.88</v>
       </c>
-      <c r="I99" s="9">
-        <f>F99-G99-H99</f>
-        <v/>
-      </c>
-      <c r="J99" s="10">
-        <f>IF(F99=0,"n.a.",(G99+H99)/F99)</f>
-        <v/>
+      <c r="I99" s="9" t="n">
+        <v>6999.999999999996</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>1.242930041700677</v>
       </c>
       <c r="K99" s="8" t="n">
         <v>0</v>
@@ -6166,13 +6014,11 @@
       <c r="H100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="9">
-        <f>F100-G100-H100</f>
-        <v/>
-      </c>
-      <c r="J100" s="10">
-        <f>IF(F100=0,"n.a.",(G100+H100)/F100)</f>
-        <v/>
+      <c r="I100" s="9" t="n">
+        <v>4914.030000000001</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>0.666706005156055</v>
       </c>
       <c r="K100" s="8" t="n">
         <v>3</v>
@@ -6224,13 +6070,11 @@
       <c r="H101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="9">
-        <f>F101-G101-H101</f>
-        <v/>
-      </c>
-      <c r="J101" s="10">
-        <f>IF(F101=0,"n.a.",(G101+H101)/F101)</f>
-        <v/>
+      <c r="I101" s="9" t="n">
+        <v>-14385.05</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>1.636085863554861</v>
       </c>
       <c r="K101" s="8" t="n">
         <v>1</v>
@@ -6282,13 +6126,11 @@
       <c r="H102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="9">
-        <f>F102-G102-H102</f>
-        <v/>
-      </c>
-      <c r="J102" s="10">
-        <f>IF(F102=0,"n.a.",(G102+H102)/F102)</f>
-        <v/>
+      <c r="I102" s="9" t="n">
+        <v>189.05</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="K102" s="8" t="n">
         <v>0</v>
@@ -6336,13 +6178,11 @@
       <c r="H103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="9">
-        <f>F103-G103-H103</f>
-        <v/>
-      </c>
-      <c r="J103" s="10">
-        <f>IF(F103=0,"n.a.",(G103+H103)/F103)</f>
-        <v/>
+      <c r="I103" s="9" t="n">
+        <v>-16812.77</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>1.537593531778502</v>
       </c>
       <c r="K103" s="8" t="n">
         <v>6</v>
@@ -6394,13 +6234,11 @@
       <c r="H104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I104" s="9">
-        <f>F104-G104-H104</f>
-        <v/>
-      </c>
-      <c r="J104" s="10">
-        <f>IF(F104=0,"n.a.",(G104+H104)/F104)</f>
-        <v/>
+      <c r="I104" s="9" t="n">
+        <v>-7561.540000000001</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>1.815037175803069</v>
       </c>
       <c r="K104" s="8" t="n">
         <v>21</v>
@@ -6452,13 +6290,11 @@
       <c r="H105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I105" s="9">
-        <f>F105-G105-H105</f>
-        <v/>
-      </c>
-      <c r="J105" s="10">
-        <f>IF(F105=0,"n.a.",(G105+H105)/F105)</f>
-        <v/>
+      <c r="I105" s="9" t="n">
+        <v>-88298.14999999999</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>1.546399240198302</v>
       </c>
       <c r="K105" s="8" t="n">
         <v>10</v>
@@ -6510,13 +6346,11 @@
       <c r="H106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I106" s="9">
-        <f>F106-G106-H106</f>
-        <v/>
-      </c>
-      <c r="J106" s="10">
-        <f>IF(F106=0,"n.a.",(G106+H106)/F106)</f>
-        <v/>
+      <c r="I106" s="9" t="n">
+        <v>-22519.56</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>5.546127338464986</v>
       </c>
       <c r="K106" s="8" t="n">
         <v>5</v>
@@ -6543,6 +6377,8 @@
         <v>0</v>
       </c>
     </row>
+    <row r="107"/>
+    <row r="108"/>
     <row r="109">
       <c r="C109" t="inlineStr">
         <is>
